--- a/src/attributions/attributions_ig_traj_102.xlsx
+++ b/src/attributions/attributions_ig_traj_102.xlsx
@@ -1568,19 +1568,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.056766620235722</v>
+        <v>0.2888599259357382</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1200731067660317</v>
+        <v>-0.2018443774393585</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1589,25 +1589,25 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01280303163801424</v>
+        <v>-0.05866559883422511</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06709257277228005</v>
+        <v>0.3582806618736658</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.07776209961929048</v>
+        <v>-0.1053319573419849</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1616,67 +1616,67 @@
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05624213229988178</v>
+        <v>-0.03971353280603539</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01721636859873661</v>
+        <v>-0.006814954467789828</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001123797568368079</v>
+        <v>-0.2310892194640037</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.007755569016272361</v>
+        <v>0.0004602533946976695</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.001386873838491958</v>
+        <v>0.08722391417452841</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0277710600404103</v>
+        <v>-0.08947653178363306</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.003142167661970363</v>
+        <v>0.04676842399027856</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.001489092223876864</v>
+        <v>0.01023038344625641</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1685,10 +1685,10 @@
         <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.002213006175287879</v>
+        <v>-0.01611749955623068</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1700,37 +1700,37 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.003565154283050078</v>
+        <v>-0.0005738693475676913</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.01566754381962761</v>
+        <v>0.1542853668163004</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.299323492205082</v>
+        <v>-0.06017701034826901</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.0351065893135112</v>
+        <v>-0.03698616082167982</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.06145136178677382</v>
+        <v>0.06018840463434003</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1739,10 +1739,10 @@
         <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1193689873566965</v>
+        <v>-0.214872191774637</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.09070860795353504</v>
+        <v>0.04359156473815901</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.03120364421319282</v>
+        <v>-0.0553464538544861</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,130 +1769,130 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1232524789931433</v>
+        <v>0.07439772610808365</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.06460478662104065</v>
+        <v>0.06702241394169033</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.01950526874364108</v>
+        <v>0.1525225185567907</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1111434336796005</v>
+        <v>-0.2523533116818283</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.06165164228563264</v>
+        <v>-0.01499172728819527</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.04026781576848353</v>
+        <v>-0.2387749756183043</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.04627067575460225</v>
+        <v>0.1347220034214815</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.01093101896865148</v>
+        <v>0.04807063411013809</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.05442185040338458</v>
+        <v>-0.2208228076076127</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0524017501112404</v>
+        <v>0.1751997794431285</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1211540400015744</v>
+        <v>-0.102446508134068</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.03411841091469072</v>
+        <v>-0.2164469063602834</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.04036200703529753</v>
+        <v>0.1054149121102184</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.003979826625424424</v>
+        <v>0.0452819274529352</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.01380359762307882</v>
+        <v>-0.2618842783480299</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -1901,37 +1901,37 @@
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04765529068147886</v>
+        <v>0.1688365479348741</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.05472478933066188</v>
+        <v>0.08594896872020762</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.002240598936297074</v>
+        <v>-0.1816958112264181</v>
       </c>
       <c r="DO3" t="n">
         <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.04018549783732978</v>
+        <v>0.3575882962060408</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,16 +1940,16 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0.01325902553476501</v>
+        <v>0.05733674393847596</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.004529716388887757</v>
+        <v>0.01883145509408578</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
@@ -1958,49 +1958,49 @@
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1072670122851758</v>
+        <v>0.4028795457737503</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.04767242894644028</v>
+        <v>-0.05377487270267575</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.05859609334362027</v>
+        <v>-0.07909734309991112</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.05139287075544744</v>
+        <v>0.01488118173985593</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02925658940106578</v>
+        <v>0.1004668763239576</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.02191480818156832</v>
+        <v>0.1107700258305928</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2009,79 +2009,79 @@
         <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1660078603219602</v>
+        <v>0.2556636795983799</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.01100763247508005</v>
+        <v>-0.1201695411880413</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.03831423213278845</v>
+        <v>-0.2133987615610407</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0603673584652324</v>
+        <v>0.0986894334014244</v>
       </c>
       <c r="FC3" t="n">
         <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.009053917323197186</v>
+        <v>0.03283513545360256</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01789910177344254</v>
+        <v>-0.2505798932677621</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.07674578530406836</v>
+        <v>0.2032409455561204</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.01627333053273798</v>
+        <v>-0.06117345085402334</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.03512073018509291</v>
+        <v>-0.01174582067400627</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
@@ -2090,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.03260180090816518</v>
+        <v>0.05387311748410794</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2105,16 +2105,16 @@
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.1246319855569738</v>
+        <v>0.2749386605219864</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.0293503169615628</v>
+        <v>-0.02500854285480824</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,16 +2123,16 @@
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0.03965597715094834</v>
+        <v>-0.06893995675704723</v>
       </c>
     </row>
     <row r="4">
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3750692905323016</v>
+        <v>0.6541860402832764</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1098071928037783</v>
+        <v>-0.283519551065073</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06569282082874191</v>
+        <v>-0.116629219608298</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,25 +2727,25 @@
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2797389432575227</v>
+        <v>0.6273608536522824</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09652777690591323</v>
+        <v>-0.3505182169374224</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06312678848588227</v>
+        <v>-0.2072910667996826</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,73 +2760,73 @@
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1094602117063855</v>
+        <v>0.0551433885628503</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.006133945073468993</v>
+        <v>0.02041277442368883</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004833944065366676</v>
+        <v>-0.08725019226484133</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06475854737020294</v>
+        <v>-0.003139744157151295</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01360874486086687</v>
+        <v>-0.1668574042068408</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.02879785908883901</v>
+        <v>-0.02016647149050158</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0214240144911415</v>
+        <v>0.0810925142001796</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005887296357415203</v>
+        <v>-0.008066760440859059</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01709753653414538</v>
+        <v>0.06018585437509682</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2844,73 +2844,73 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3886461911272258</v>
+        <v>0.6105815068552072</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01421644314176461</v>
+        <v>-0.179191320912695</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.03878646979524958</v>
+        <v>-0.1297278897959862</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03551732653820464</v>
+        <v>0.06101683942575555</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.06327490955793313</v>
+        <v>-0.009556951898427214</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1421314518624072</v>
+        <v>-0.04287613142857726</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03908018453641142</v>
+        <v>-0.1861281356776025</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.08755970565128356</v>
+        <v>0.03678935717396421</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1513964436726919</v>
+        <v>0.1487879183716585</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2922,100 +2922,100 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1648071342987789</v>
+        <v>0.3795868306895557</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.009366966538815432</v>
+        <v>-0.1528860401647285</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.02564809999495884</v>
+        <v>0.03200744250784015</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1213445304252127</v>
+        <v>-0.3164112399318982</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02709147205550789</v>
+        <v>0.2255400564136322</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02679990760843733</v>
+        <v>0.01121497674844317</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02440029191226319</v>
+        <v>-0.2384999096758846</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06392629774987216</v>
+        <v>0.2124628634636213</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1258932385586478</v>
+        <v>-0.09819321687744283</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.102506255256207</v>
+        <v>-0.3118764658213303</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.05704271280668137</v>
+        <v>0.200149686166151</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03438032716029957</v>
+        <v>0.05070881620153121</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3027,52 +3027,52 @@
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1270074676053644</v>
+        <v>-0.150724269901701</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.05839932418352745</v>
+        <v>0.03898136807007081</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.003509664713362442</v>
+        <v>-0.2281828155693197</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01994782902640184</v>
+        <v>0.2346918496709917</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.1036815732991094</v>
+        <v>-0.1576292456677247</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.03053008798281204</v>
+        <v>0.02383469984662291</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3084,52 +3084,52 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.09938733667834035</v>
+        <v>0.02722282065211808</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.04977280052672513</v>
+        <v>0.1598239953050297</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0152102918104059</v>
+        <v>0.08815767747254512</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1208079236070438</v>
+        <v>-0.2814193968528476</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0597414142897584</v>
+        <v>0.1715281957126247</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.06577653746364566</v>
+        <v>0.1219385477150179</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -3141,22 +3141,22 @@
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.07581012933029899</v>
+        <v>-0.1248695284042699</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.04861210161536125</v>
+        <v>0.04413126817801398</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.005690246359806251</v>
+        <v>-0.04557967135066111</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,109 +3165,109 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1137081804600303</v>
+        <v>-0.3454322292606865</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03477884380831831</v>
+        <v>0.2355692654353874</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.03009057599324769</v>
+        <v>-0.002971282187048283</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02147060240110048</v>
+        <v>-0.2004767235620529</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.03723507758488112</v>
+        <v>0.07091286599430606</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.07336868358566011</v>
+        <v>-0.09573966221182365</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.03331050794147346</v>
+        <v>-0.3037817536717898</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.08873709843446376</v>
+        <v>0.4077298478399522</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.004766514525127976</v>
+        <v>0.1802246422504896</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.04710481570056813</v>
+        <v>-0.3253452905952619</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.05848724505155706</v>
+        <v>0.1598789293189019</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1791890193668759</v>
+        <v>0.6822810325040551</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1036774208416298</v>
+        <v>0.07262319601116293</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01883358422271386</v>
+        <v>-0.2773006009845363</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -3302,79 +3302,79 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1312432502246612</v>
+        <v>0.75162709299879</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09459728369043592</v>
+        <v>-0.1024918979565595</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02702070352734265</v>
+        <v>-0.2102771859061154</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04554621490419106</v>
+        <v>0.1180139017982213</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.05694229937950181</v>
+        <v>-0.09319181108283338</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002636091047033378</v>
+        <v>-0.07835154000289596</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05883115137858293</v>
+        <v>0.01570643009747502</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.009728643158971158</v>
+        <v>-0.1668500573401563</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.02023562476975401</v>
+        <v>-0.01460677887512377</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.03296270268861795</v>
+        <v>0.09050630935614341</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.006149987785331082</v>
+        <v>0.03198192281282197</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01229557571113286</v>
+        <v>-0.02095087961096354</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,64 +3410,64 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2933558124102254</v>
+        <v>0.9324518508298727</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01753119131749688</v>
+        <v>-0.1222448122020432</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01452141809048589</v>
+        <v>-0.1187010484763021</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01908438074641036</v>
+        <v>-0.005953899205523088</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1169893903789226</v>
+        <v>-0.06774192586424178</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01407761763728289</v>
+        <v>-0.1669025292804504</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.09853470294003398</v>
+        <v>-0.07342838134853327</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.07576334780354999</v>
+        <v>0.1331467992162435</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.07545505692123664</v>
+        <v>0.0528775787922807</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3488,25 +3488,25 @@
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.08562614186713045</v>
+        <v>0.3919915538785852</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.002763270829341916</v>
+        <v>-0.0101409487757968</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.007492017915094996</v>
+        <v>-0.1744465515713003</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,13 +3515,13 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.04779623561350402</v>
+        <v>-0.31923847197781</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,67 +3530,67 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.02260542189778206</v>
+        <v>-0.03351199884580072</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.004963260910253799</v>
+        <v>0.1591886457190096</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.03319345467049338</v>
+        <v>-0.2165118283774806</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.04292548631964083</v>
+        <v>0.1121767467463406</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.03668463333351432</v>
+        <v>0.1560947128643611</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.03410947638499571</v>
+        <v>-0.3079542888862876</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01482137326436262</v>
+        <v>-0.0219325452375341</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02783452601687194</v>
+        <v>0.1777159917617485</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,52 +3602,52 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.05696039469788408</v>
+        <v>-0.1186017120275896</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1207085559323514</v>
+        <v>-0.3198849104158362</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.01241463895055945</v>
+        <v>0.08316382286843954</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
         <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.03487206596248227</v>
+        <v>0.09270166394162331</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.1356031073027568</v>
+        <v>0.06171106333337966</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.06173349243006124</v>
+        <v>-0.03502371333241389</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3656,19 +3656,19 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.03778016469743672</v>
+        <v>-0.0570269057304378</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.03563286987827287</v>
+        <v>-0.1062049831770455</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.007061481230329616</v>
+        <v>0.08828345628608172</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3680,25 +3680,25 @@
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.04895667971849671</v>
+        <v>-0.2026566328930178</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02340219802574454</v>
+        <v>-0.04695594826183527</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0136314189474123</v>
+        <v>0.1125917603891995</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,37 +3707,37 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04280658781609475</v>
+        <v>-0.1357814480632874</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02226181224229525</v>
+        <v>-0.1196058050014169</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0184084446771826</v>
+        <v>0.05870706331101225</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.03287607489784305</v>
+        <v>-0.3347269944249298</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,13 +3746,13 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.006481124818407748</v>
+        <v>-0.1030596716827119</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03332281950961164</v>
+        <v>0.1519087927474541</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3764,73 +3764,73 @@
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01309244811874139</v>
+        <v>-0.318868236325189</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.1125026128045538</v>
+        <v>0.06806824596240195</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02579419793779778</v>
+        <v>0.2534048615200539</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01246894457901271</v>
+        <v>-0.3305652565953451</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.05714908897386962</v>
+        <v>-0.07802988646754754</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.03323970029058822</v>
+        <v>-0.01006537803141986</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01686129740215952</v>
+        <v>-0.1617435358482985</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.05978105399168301</v>
+        <v>0.1349907744161339</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,24 +3839,24 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.6328075717605904</v>
+        <v>-0.6321809926581313</v>
       </c>
       <c r="C7" t="n">
         <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.919621423769197</v>
+        <v>0.4397485102092213</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08233009600943182</v>
+        <v>0.2391358042773888</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -3871,19 +3871,19 @@
         <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6893569303881576</v>
+        <v>-0.8446648405162875</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7527522015363804</v>
+        <v>0.5961916140165262</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04594422959528578</v>
+        <v>0.3334327022345134</v>
       </c>
       <c r="O7" t="n">
         <v>-0</v>
@@ -3901,25 +3901,25 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2194873083393752</v>
+        <v>-0.08723486348007077</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2191490137926542</v>
+        <v>-0.004138123638940634</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.939171659588502e-05</v>
+        <v>0.07331446554283239</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>-0</v>
@@ -3928,22 +3928,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.074399040149864</v>
+        <v>-0.005108459182532723</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1078105399068023</v>
+        <v>0.06327343091744478</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.008739256975897348</v>
+        <v>0.00134902305640901</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.06338055147709901</v>
+        <v>-0.117416511591606</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.03225309881062687</v>
+        <v>0.04565390458228732</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08283651008794267</v>
+        <v>-0.1463895417188938</v>
       </c>
       <c r="AP7" t="n">
         <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3982,46 +3982,46 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.3221538849292315</v>
+        <v>-0.601151398726535</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.5394717345129427</v>
+        <v>0.3725713585613616</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1347021993847498</v>
+        <v>0.1994855818971978</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.279971477636451</v>
+        <v>0.1317283268290048</v>
       </c>
       <c r="BE7" t="n">
         <v>-0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.319201927818603</v>
+        <v>-0.0363973089434118</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.05050918703817869</v>
+        <v>0.1431821460728634</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI7" t="n">
         <v>0</v>
@@ -4033,19 +4033,19 @@
         <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.1580084179708709</v>
+        <v>0.1566580654495428</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.04345231467231404</v>
+        <v>-0.0842437888599735</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.2752654305382655</v>
+        <v>-0.1279281826229909</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.2663490468937174</v>
+        <v>-0.6311638458126023</v>
       </c>
       <c r="BW7" t="n">
         <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.2829904158107518</v>
+        <v>0.320415967773499</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.03677480927812671</v>
+        <v>0.002734267177097111</v>
       </c>
       <c r="BZ7" t="n">
         <v>-0</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
@@ -4090,100 +4090,100 @@
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1490908684111807</v>
+        <v>0.3742117034048665</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.2753960648454608</v>
+        <v>-0.227036125936008</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02848631330485429</v>
+        <v>-0.03259293030116946</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
         <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.07109916620238942</v>
+        <v>0.2880033018460811</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.03671265128667765</v>
+        <v>-0.2576712071872818</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.09057304772339081</v>
+        <v>0.01512233341985883</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.1726648403190322</v>
+        <v>0.3775241644170938</v>
       </c>
       <c r="CX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.2742845177214312</v>
+        <v>-0.2237015435724685</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.05527842215839497</v>
+        <v>-0.07260653217487233</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
         <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.4119086775983209</v>
+        <v>0.2405702541634882</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.2706215557381905</v>
+        <v>-0.1479738556580606</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01027545256276195</v>
+        <v>0.233894853323818</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK7" t="n">
         <v>-0</v>
@@ -4192,25 +4192,25 @@
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07374745620877896</v>
+        <v>-0.2691755465205819</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.02851845555687152</v>
+        <v>-0.06746333843718574</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.15930060732892</v>
+        <v>-0.03770902643133727</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -4222,46 +4222,46 @@
         <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.1211601905513583</v>
+        <v>-0.014374484828515</v>
       </c>
       <c r="DY7" t="n">
         <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.199385159289232</v>
+        <v>-0.07648528920161059</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.1316032290837519</v>
+        <v>0.02742789674119211</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.1353972885482504</v>
+        <v>0.3611876614872565</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.2040053976424784</v>
+        <v>-0.2211062768212405</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.07506379592730614</v>
+        <v>-0.1092200231474598</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.1487716209758493</v>
+        <v>0.1695748906763187</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.17413840263391</v>
+        <v>0.1769198763304735</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.02706226988742523</v>
+        <v>-0.02373047456609876</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
         <v>-0</v>
@@ -4306,52 +4306,52 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.1581871973232214</v>
+        <v>0.4160128497503978</v>
       </c>
       <c r="EZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.2649379656768466</v>
+        <v>-0.2511904446283909</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.009227756810237178</v>
+        <v>-0.02305176655787037</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03344265572748829</v>
+        <v>0.2071648613548529</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.06879078898982426</v>
+        <v>-0.1197349919339116</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02127471863598579</v>
+        <v>0.03185203117577074</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
@@ -4360,16 +4360,16 @@
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.09298720668386182</v>
+        <v>0.2690271179631386</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.1238882254566603</v>
+        <v>-0.4761814779774032</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04201820475586302</v>
+        <v>-0.2047940179059483</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,37 +4378,37 @@
         <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
         <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1911555458704438</v>
+        <v>0.3360532816480812</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.06573414354921815</v>
+        <v>-0.1320674120617943</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE7" t="n">
         <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,16 +4416,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.299265586680134</v>
+        <v>0.8995426857186731</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04693620392050294</v>
+        <v>-0.4532264003812522</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.067933123425026</v>
+        <v>-0.1918028735659179</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4434,25 +4434,25 @@
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1846472005117162</v>
+        <v>0.9825715505087396</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06919256953552069</v>
+        <v>-0.5958853885722637</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.05813342018922582</v>
+        <v>-0.3021166519789264</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4470,151 +4470,151 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05525603293176527</v>
+        <v>0.1444860423343858</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.02168831399165951</v>
+        <v>-0.09214627366376517</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03707796950195311</v>
+        <v>-0.06277980163508287</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01411563728668376</v>
+        <v>0.1976265487024904</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01380443834273964</v>
+        <v>-0.1443204112161751</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.006734300810716519</v>
+        <v>0.1595715680405157</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.006067770872468084</v>
+        <v>0.1475451217781973</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.02242417973434365</v>
+        <v>-0.0943535227055859</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.03565830017402458</v>
+        <v>0.1794633198465971</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2739515961133757</v>
+        <v>1.084280253259032</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.05756479279642681</v>
+        <v>-0.3213324290291241</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.07068812764616561</v>
+        <v>-0.1681919306540468</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03275042517779055</v>
+        <v>-0.05781825125469212</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0863375614014957</v>
+        <v>-0.05529732831297884</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.08612348833338436</v>
+        <v>-0.1540916207012965</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1116991400380274</v>
+        <v>-0.04533378195632965</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.03527147595456146</v>
+        <v>0.03566232097257236</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1370185547341826</v>
+        <v>0.2417658238508092</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4629,100 +4629,100 @@
         <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1152128444184044</v>
+        <v>0.5718461388712822</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0218939354372459</v>
+        <v>-0.2193388225637422</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.04317800306220474</v>
+        <v>0.02316993907790417</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.07652423617752666</v>
+        <v>-0.4099138971401083</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.003730555700401604</v>
+        <v>0.2907418290945397</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.009976103200564843</v>
+        <v>0.01329568783570815</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01469344992661958</v>
+        <v>-0.4017249707966941</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.04117071468862703</v>
+        <v>0.3229348428215589</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.07985462787776454</v>
+        <v>-0.1330681409127903</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.0632711461047014</v>
+        <v>-0.4139288535900809</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.008531679948082332</v>
+        <v>0.2999816443588588</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01012609869331032</v>
+        <v>0.04401329748831042</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
@@ -4731,25 +4731,25 @@
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.079958394371945</v>
+        <v>-0.2384308499529776</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.06013847645755621</v>
+        <v>0.1195979602547665</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05143794405254809</v>
+        <v>-0.1812653891010586</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
@@ -4764,22 +4764,22 @@
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.03720864795935457</v>
+        <v>-0.3235467003505824</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0631199956273083</v>
+        <v>-0.2109540377982582</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.03435450012509403</v>
+        <v>-0.05847359951233064</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4794,76 +4794,76 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.07573262094394267</v>
+        <v>-0.2533247574065657</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.03223510503698678</v>
+        <v>0.149673308288964</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.03064952522744653</v>
+        <v>0.1318000059288194</v>
       </c>
       <c r="EB8" t="n">
         <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08574883047727083</v>
+        <v>-0.381851973767139</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.01449832091944414</v>
+        <v>0.2422348811847402</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.04711581098584234</v>
+        <v>0.1743152274035259</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01498707986727341</v>
+        <v>0.02137129424560504</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.0145235238797208</v>
+        <v>0.1162003026915347</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.05362607232152682</v>
+        <v>-0.05784264001089991</v>
       </c>
       <c r="ET8" t="n">
         <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,16 +4875,16 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.06261537891203178</v>
+        <v>-0.4753654764545323</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>-0.008808746715833564</v>
+        <v>0.3376338309814964</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01042736011382061</v>
+        <v>-0.0008177667018233812</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
@@ -4893,25 +4893,25 @@
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.01572851417048864</v>
+        <v>-0.1118109768149922</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.01125570738825849</v>
+        <v>0.1396189517787943</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.07592520393421852</v>
+        <v>-0.3122063471241574</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
@@ -4923,22 +4923,22 @@
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.03818855874827026</v>
+        <v>-0.5498346413561167</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.05339004230419584</v>
+        <v>0.3232730827066409</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.04687313574317486</v>
+        <v>0.3926872536946026</v>
       </c>
       <c r="FU8" t="n">
         <v>-0</v>
@@ -4947,34 +4947,34 @@
         <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.02003839716673314</v>
+        <v>-0.3243107137083605</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.06480393895651977</v>
+        <v>0.1717370634352205</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
         <v>-0</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4982,22 +4982,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.07868907907439222</v>
+        <v>-0.07413198328658827</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03020546802347933</v>
+        <v>-0.05414514830899651</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7527727463828314</v>
+        <v>0.2326177389654963</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5009,25 +5009,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0235316238447484</v>
+        <v>-0.1089824554237653</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09919713077052668</v>
+        <v>-0.03277008515276033</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5289528840732353</v>
+        <v>0.2575647400942377</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -5036,22 +5036,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
         <v>-0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01952049608365359</v>
+        <v>-0.007777788962668853</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09272195778701957</v>
+        <v>-0.009274562807611851</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1114970081459236</v>
+        <v>0.01584932242898301</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
@@ -5072,16 +5072,16 @@
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.03983598077799074</v>
+        <v>0.03857503051928036</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0167412258657288</v>
+        <v>0.06456610325316854</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.03974145177323759</v>
+        <v>0.01919244069218087</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
         <v>-0</v>
@@ -5099,19 +5099,19 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0219598783450621</v>
+        <v>0.01496779942358438</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.06703260458859499</v>
+        <v>-0.02873721142711723</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.04010054252485149</v>
+        <v>-0.01227336285662643</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>-0</v>
@@ -5123,55 +5123,55 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.03471908338935103</v>
+        <v>-0.04057003394751662</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08591846857223356</v>
+        <v>-0.128672476021512</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.5028812865257449</v>
+        <v>0.1674137639693096</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01599588157737961</v>
+        <v>0.005132048155667623</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00591403073756467</v>
+        <v>0.05923772011215589</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.2343137635559444</v>
+        <v>0.01601401914121145</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
@@ -5180,19 +5180,19 @@
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1214902422529187</v>
+        <v>0.04932894041807808</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.06256434783013555</v>
+        <v>-0.091638708483625</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0.001007833550742547</v>
+        <v>-0.039675163438044</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
         <v>-0</v>
@@ -5207,16 +5207,16 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.01076213647635541</v>
+        <v>-0.1000754430577907</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0823500166576174</v>
+        <v>-0.1146021019704771</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.2724551508062036</v>
+        <v>0.1262914846691176</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0211788015283778</v>
+        <v>0.0275456468849377</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02131592864720182</v>
+        <v>0.0298401668380962</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0.204088339637019</v>
+        <v>-0.06734076430991867</v>
       </c>
       <c r="CJ9" t="n">
         <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5261,25 +5261,25 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1022380795041846</v>
+        <v>0.003654218062810484</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.2208022913110022</v>
+        <v>0.06016316480455532</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.06127556238283538</v>
+        <v>0.006197034640768942</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
         <v>-0</v>
@@ -5288,25 +5288,25 @@
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02850806749408282</v>
+        <v>0.02775511233001418</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01917979576260849</v>
+        <v>0.01612681064920963</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0.1851975425623336</v>
+        <v>-0.08694776494778805</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
         <v>-0</v>
@@ -5315,13 +5315,13 @@
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01549144829642637</v>
+        <v>0.03533585255951868</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.05532242310439797</v>
+        <v>-0.1416061032153533</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.00102135377306475</v>
+        <v>-0.000455405916732679</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -5330,28 +5330,28 @@
         <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
         <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05053929646097749</v>
+        <v>-0.02363949284674229</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02702795515825224</v>
+        <v>-0.003344232548581641</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.08956001809054782</v>
+        <v>0.006178031967802541</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -5363,49 +5363,49 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01981571923388522</v>
+        <v>0.01414865385354508</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.007335904036208227</v>
+        <v>0.0739570594498424</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.121870891058855</v>
+        <v>0.08844683490383706</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.1012159837794926</v>
+        <v>0.05240393440799419</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03234475734797808</v>
+        <v>0.00834840772860284</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0.1475008969742896</v>
+        <v>-0.01719634638613985</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
@@ -5414,34 +5414,34 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.08137739321394864</v>
+        <v>0.03066167324704026</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01535506074525002</v>
+        <v>0.09750725765830799</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.03215612785943334</v>
+        <v>-0.03950348709179192</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
         <v>0</v>
@@ -5450,100 +5450,100 @@
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03343460464020962</v>
+        <v>0.0386151110579356</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.05869474687463309</v>
+        <v>0.02348971847843925</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0.1748987783846957</v>
+        <v>-0.08448679335558276</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0.04568243883160864</v>
+        <v>0.06050072328005056</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.07996845320556581</v>
+        <v>0.04167441062843232</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.1219955097058661</v>
+        <v>-0.03663308377137963</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.01022718428135069</v>
+        <v>-0.02913547285772028</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.2854336114391771</v>
+        <v>0.2096571564020568</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0.09466958199299466</v>
+        <v>-0.03031677848610569</v>
       </c>
       <c r="FV9" t="n">
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.009567948898950017</v>
+        <v>0.08225987211686434</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.005362931499741571</v>
+        <v>-0.0258395845113884</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5528775001402585</v>
+        <v>0.5372669367838552</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01453760429325892</v>
+        <v>-0.03880962490593891</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4667893949817093</v>
+        <v>-0.2165676912210912</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.417684068809007</v>
+        <v>0.8888758201271137</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.02508747765506329</v>
+        <v>-0.162160455937545</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5132373770722745</v>
+        <v>-0.3014665486293167</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08355225222456056</v>
+        <v>0.1920707444627073</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01937822669010482</v>
+        <v>-0.1943814002763433</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002658846508433222</v>
+        <v>-0.01481640218773005</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05032154152566831</v>
+        <v>0.02915931079150896</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0452238122739473</v>
+        <v>-0.4325883087767034</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.0006138402386187273</v>
+        <v>-0.177116916761541</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04783611672034568</v>
+        <v>0.07100156034737894</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01105260176864441</v>
+        <v>-0.08751197442812333</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.09245244625987968</v>
+        <v>-0.02977348530376467</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4422955460039922</v>
+        <v>0.8999644060588265</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02909958576290571</v>
+        <v>-0.1899572132058835</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.3422947096666415</v>
+        <v>-0.2877109438313255</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,34 +7423,34 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1729184930104705</v>
+        <v>-0.005223259764982567</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1709748528180153</v>
+        <v>-0.2153987441247562</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.205773175343103</v>
+        <v>-0.03537888606564646</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.2002558661155981</v>
+        <v>0.1625552795285686</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1039353742559497</v>
+        <v>0.1334187614211437</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.002745880478777002</v>
+        <v>-0.06333506881801695</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,19 +7477,19 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2202303488753476</v>
+        <v>0.5756790283571528</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02337664209677967</v>
+        <v>-0.0938506414998475</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1318044597539551</v>
+        <v>-0.1261243686077028</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7501,10 +7501,10 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1021583914261066</v>
+        <v>-0.1877970269757799</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
@@ -7513,40 +7513,40 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.03532466201889423</v>
+        <v>0.07072009622528989</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08458899011131685</v>
+        <v>0.1182252210332908</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.07622266115666991</v>
+        <v>-0.5349070891209067</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0557340921369089</v>
+        <v>0.2613966506117856</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.008414755707959833</v>
+        <v>0.1436572325526864</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,10 +7555,10 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07580754175083776</v>
+        <v>-0.1837415808611344</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,16 +7567,16 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02465610247676257</v>
+        <v>0.01415621034023193</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08176320215717549</v>
+        <v>0.1203172450526309</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,19 +7585,19 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1214138544860826</v>
+        <v>-0.01548987196528341</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05060995353399975</v>
+        <v>-0.3361774532384811</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.007237652848752282</v>
+        <v>-0.07234625705639779</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
@@ -7606,52 +7606,52 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.04239344016925617</v>
+        <v>-0.1961143727728041</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0009569524015280327</v>
+        <v>0.1601952295190031</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01339061053045242</v>
+        <v>0.008637814132485554</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.04107505515408476</v>
+        <v>0.02111319435408945</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.01863605066313381</v>
+        <v>0.2111101787924141</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.007276819296266104</v>
+        <v>-0.1987076781484413</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7663,25 +7663,25 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.04617767171618136</v>
+        <v>-0.0003812455635604469</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.0003742366308802584</v>
+        <v>-0.08326424169214684</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.06937071822897516</v>
+        <v>0.07005540656746991</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7690,10 +7690,10 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03578639701946226</v>
+        <v>0.06901766726315298</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,10 +7702,10 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.002511782053140976</v>
+        <v>-0.1008289781629941</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01378986376957782</v>
+        <v>0.06916514146792992</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.07548832889363698</v>
+        <v>-0.2103276517476383</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.007989336884898357</v>
+        <v>0.007225353350047363</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.08253256689453026</v>
+        <v>0.1204409276804921</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02667509012319998</v>
+        <v>-0.2622215421380676</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.03698981378461119</v>
+        <v>0.2496844999611798</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.1252882643213336</v>
+        <v>0.02027647527075637</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.003006450450050371</v>
+        <v>0.06000953316141198</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,37 +7783,37 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.07167172005777364</v>
+        <v>-0.07758732239638148</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.08244596212143086</v>
+        <v>-0.1283755579371373</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.04856345833787983</v>
+        <v>-2.288541360379644e-05</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.09574389797521202</v>
+        <v>-0.002258283347948613</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7827,82 +7827,82 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.3215455388035593</v>
+        <v>-0.4531832812081955</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4268003676076384</v>
+        <v>0.4837608259379137</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04173892244839422</v>
+        <v>0.3168489085064923</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2718347124616217</v>
+        <v>-0.5024710680868091</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3772290778366779</v>
+        <v>0.6577634221555146</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1040416034487176</v>
+        <v>0.4805985969219609</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.05004081533165394</v>
+        <v>-0.07644077401021288</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1090151972643475</v>
+        <v>0.08424555629939109</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1506715327024163</v>
+        <v>0.03274160387450207</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
@@ -7911,43 +7911,43 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.02887431776891015</v>
+        <v>0.005730420394870558</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.03099607481832935</v>
+        <v>-0.0161548377051621</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.002171664272443816</v>
+        <v>-0.100147824757869</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.0539421869878648</v>
+        <v>-0.1996210686626445</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.03142291941106781</v>
+        <v>0.03266718695219852</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.02255053611939785</v>
+        <v>-0.1979816155410517</v>
       </c>
       <c r="AP14" t="n">
         <v>-0</v>
@@ -7965,43 +7965,43 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.4019385659229635</v>
+        <v>-0.5774974535069796</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.06897792228284406</v>
+        <v>0.09699505135435685</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1281272531239209</v>
+        <v>0.2495775368474911</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.02430147668617014</v>
+        <v>0.05949699014797669</v>
       </c>
       <c r="BE14" t="n">
         <v>-0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.1903385692718083</v>
+        <v>0.2126817940117039</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.2738649758045769</v>
+        <v>0.2492155149044933</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
@@ -8019,19 +8019,19 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.03628727823673479</v>
+        <v>0.0894868880036527</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.001377243529933103</v>
+        <v>-0.08749210577363288</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.08873255418709254</v>
+        <v>-0.04476900226085904</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8046,46 +8046,46 @@
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.2477178503924696</v>
+        <v>-0.4344969099678129</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.05550396287344841</v>
+        <v>0.2815807230769858</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.004352928206524021</v>
+        <v>0.1000106632888934</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
         <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.08573867346287942</v>
+        <v>0.2864744914409602</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.09433899030873051</v>
+        <v>-0.1694479530507532</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0242901099866377</v>
+        <v>-0.01999625383159155</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>0</v>
@@ -8100,19 +8100,19 @@
         <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.02291582543317137</v>
+        <v>0.2280260382961562</v>
       </c>
       <c r="CO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.04344608758541615</v>
+        <v>-0.3669643868573721</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.0102587016080173</v>
+        <v>-0.1328837451241059</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
@@ -8121,22 +8121,22 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.08070271466793195</v>
+        <v>0.274744490258868</v>
       </c>
       <c r="CX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.09078368292945241</v>
+        <v>-0.1901359838881012</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.007199192679304272</v>
+        <v>-0.05261814035989516</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8151,22 +8151,22 @@
         <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.007633889506394685</v>
+        <v>0.005382956578433446</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.04186968986327556</v>
+        <v>-0.07210540266974642</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.0798733474127364</v>
+        <v>0.07976195286211725</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8178,25 +8178,25 @@
         <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.06040769406593899</v>
+        <v>0.1069822892894526</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.1282058627817134</v>
+        <v>-0.1330042773840573</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.003082269080396409</v>
+        <v>0.05259537213572242</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
@@ -8205,46 +8205,46 @@
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.01187928681479571</v>
+        <v>-0.06280648897785196</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.007776695515561097</v>
+        <v>-0.04664092751532871</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01436470848984942</v>
+        <v>-0.09587447513027886</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
         <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.008623267379450121</v>
+        <v>0.2380334424395218</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.03287586678445679</v>
+        <v>-0.07562141415390744</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.02019692815802627</v>
+        <v>-0.119961558994652</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8253,31 +8253,31 @@
         <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.08328260824759384</v>
+        <v>0.2151974317109577</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.06429325396644589</v>
+        <v>-0.1472405031280093</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.06278479355845612</v>
+        <v>-0.05650369024290513</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>-0</v>
@@ -8286,19 +8286,19 @@
         <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.08903957109298768</v>
+        <v>0.3169804486597755</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.09463752330257852</v>
+        <v>-0.2297463173006575</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01800727865349654</v>
+        <v>-0.04668581551134547</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
@@ -8310,31 +8310,31 @@
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0414521633608991</v>
+        <v>0.1636906759610375</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.04354840130687807</v>
+        <v>0.1627733883853974</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03291359847804542</v>
+        <v>-0.05590803395578389</v>
       </c>
       <c r="FL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,16 +8343,16 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.01221464163930013</v>
+        <v>-0.1994396429015716</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.02831107797667131</v>
+        <v>-0.1246075097004791</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01839111089489138</v>
+        <v>-0.003619124464162399</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
@@ -8361,22 +8361,22 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.06933134074777453</v>
+        <v>0.1794520301620204</v>
       </c>
       <c r="GA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.06106598869935288</v>
+        <v>-0.1186795538729922</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
@@ -8396,19 +8396,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4984606456358585</v>
+        <v>-0.4967447287547417</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1630556590172297</v>
+        <v>0.4703860228028513</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1726498722410141</v>
+        <v>0.07931035731583583</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8426,16 +8426,16 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3279555481603417</v>
+        <v>-0.4632402570887008</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1702610439958268</v>
+        <v>0.6546953481082753</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09870378554691323</v>
+        <v>0.1207738151519414</v>
       </c>
       <c r="O15" t="n">
         <v>-0</v>
@@ -8450,46 +8450,46 @@
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.04977107854097373</v>
+        <v>-0.01924964972915242</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.07105694791705165</v>
+        <v>0.05746259285113228</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1314246000310552</v>
+        <v>0.03126227931293323</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.008674013499658548</v>
+        <v>-0.01545113800665792</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1101794412399949</v>
+        <v>0.1407706950396675</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02797574269990794</v>
+        <v>-0.168073011833145</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -8498,25 +8498,25 @@
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.06945021309965831</v>
+        <v>-0.1843193915870669</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.01504631513886189</v>
+        <v>0.06962824870048588</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.08275532588214642</v>
+        <v>-0.2472024355181901</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
@@ -8534,22 +8534,22 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.2217662334140048</v>
+        <v>-0.2938530699010106</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09189041611866648</v>
+        <v>0.2402350319047131</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1593328705998186</v>
+        <v>0.1164195965981216</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
         <v>-0</v>
@@ -8558,52 +8558,52 @@
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.1701912849948955</v>
+        <v>0.04532219281538906</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1496924177117338</v>
+        <v>0.0817351347888019</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1637932605620342</v>
+        <v>0.104446135131501</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
         <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.01750633267065132</v>
+        <v>0.1583519945794504</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.02805024861406306</v>
+        <v>-0.04052267095353973</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.0150707712974798</v>
+        <v>0.03438608857713858</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
@@ -8612,19 +8612,19 @@
         <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.1869627900357449</v>
+        <v>-0.2508366729377684</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.08269522822173711</v>
+        <v>0.1920874656493603</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.07160141034564049</v>
+        <v>-0.004928790616186646</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8642,22 +8642,22 @@
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.07314132801364766</v>
+        <v>0.2258789395106455</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.04829610327900825</v>
+        <v>-0.1437682519042735</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0220016211943641</v>
+        <v>0.0350637053571804</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
@@ -8669,19 +8669,19 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.07464434621248818</v>
+        <v>0.09343133718128831</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.1890121403656911</v>
+        <v>-0.2379759972864895</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.0002884619474195425</v>
+        <v>-0.1171308587482566</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV15" t="n">
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.08217006691740611</v>
+        <v>0.2361100071935326</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.03760318759258864</v>
+        <v>-0.1569364090107236</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.006921899711900212</v>
+        <v>0.005021504899417766</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8723,16 +8723,16 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1409288196047623</v>
+        <v>0.09291384842058308</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.06822517556188347</v>
+        <v>-0.07721758768425871</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.005384569511356482</v>
+        <v>0.03068283112069992</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
@@ -8744,25 +8744,25 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.007838807386637002</v>
+        <v>0.1088648026341609</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.022049683320956</v>
+        <v>-0.08444229410637363</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04447367122941184</v>
+        <v>0.05758920467558059</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
@@ -8774,22 +8774,22 @@
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.1093686026545412</v>
+        <v>0.06061771148596962</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.0463918430016036</v>
+        <v>0.01137472661927157</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.00413492236823502</v>
+        <v>-0.013285228916829</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,49 +8804,49 @@
         <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05744850113713924</v>
+        <v>0.2391866318360412</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.05538835150769398</v>
+        <v>-0.1156661667629101</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.06456316018268303</v>
+        <v>-0.03179647219976433</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.02534774737078672</v>
+        <v>0.1637315641077234</v>
       </c>
       <c r="EQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0.05251768604493646</v>
+        <v>-0.09266773936223631</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.002826237861208346</v>
+        <v>-0.07411087057056909</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
         <v>-0</v>
@@ -8858,73 +8858,73 @@
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.08255266764086829</v>
+        <v>0.2596140822925206</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.02979239188072513</v>
+        <v>-0.18217927923712</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.02332877836078678</v>
+        <v>0.01939002663553602</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.04531463150076858</v>
+        <v>-0.09337689124888997</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.04543308323280197</v>
+        <v>0.1750441343891178</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.0177003039992163</v>
+        <v>-0.1912235224561148</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.1238616740461258</v>
+        <v>0.1644657810984315</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.08138835912372706</v>
+        <v>-0.01673281538376196</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.1981051395525977</v>
+        <v>-0.3075993929965953</v>
       </c>
       <c r="FU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
@@ -8939,25 +8939,25 @@
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.008877747759138481</v>
+        <v>0.2239425198180413</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.01675310711426355</v>
+        <v>-0.07037003541547156</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
